--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -95,6 +95,15 @@
   </si>
   <si>
     <t>Dungeon4</t>
+  </si>
+  <si>
+    <t>Null</t>
+  </si>
+  <si>
+    <t>フリーギターサウンド</t>
+  </si>
+  <si>
+    <t>https://free-guitar-sounds.work/</t>
   </si>
   <si>
     <t>Dungeon5</t>
@@ -249,10 +258,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -278,6 +287,134 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -285,134 +422,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -423,13 +432,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,49 +498,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,13 +576,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -514,96 +613,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,30 +623,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -656,26 +641,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -699,7 +675,40 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -722,7 +731,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -731,140 +740,140 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -872,6 +881,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="10" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="10">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1437,7 +1449,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>1040</v>
       </c>
@@ -1445,16 +1457,22 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>0.6</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1462,10 +1480,10 @@
         <v>1050</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D12">
         <v>0.7</v>
@@ -1485,10 +1503,10 @@
         <v>1060</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>0.5</v>
@@ -1505,10 +1523,10 @@
         <v>1210</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -1525,10 +1543,10 @@
         <v>1510</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D15">
         <v>0.6</v>
@@ -1545,10 +1563,10 @@
         <v>2010</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1560,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1568,10 +1586,10 @@
         <v>2020</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D17">
         <v>0.6</v>
@@ -1588,10 +1606,10 @@
         <v>2030</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D18">
         <v>0.8</v>
@@ -1608,10 +1626,10 @@
         <v>2040</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D19">
         <v>0.6</v>
@@ -1628,10 +1646,10 @@
         <v>3010</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1643,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1651,10 +1669,10 @@
         <v>3020</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D21">
         <v>0.6</v>
@@ -1671,10 +1689,10 @@
         <v>3030</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D22">
         <v>0.6</v>
@@ -1691,10 +1709,10 @@
         <v>4010</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D23">
         <v>0.6</v>
@@ -1711,10 +1729,10 @@
         <v>4020</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>0.6</v>
@@ -1726,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1737,10 +1755,10 @@
         <v>4030</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D25">
         <v>0.5</v>
@@ -1752,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" t="s">
         <v>57</v>
-      </c>
-      <c r="I25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1763,10 +1781,10 @@
         <v>4040</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D26">
         <v>0.5</v>
@@ -1778,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1786,10 +1804,10 @@
         <v>4050</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D27">
         <v>0.5</v>
@@ -1801,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1809,10 +1827,10 @@
         <v>4060</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D28">
         <v>0.5</v>
@@ -1829,10 +1847,10 @@
         <v>4070</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D29">
         <v>0.5</v>
@@ -1844,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1852,10 +1870,10 @@
         <v>4080</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D30">
         <v>0.5</v>
@@ -1867,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1878,10 +1896,10 @@
         <v>4090</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D31">
         <v>0.5</v>
@@ -1893,10 +1911,10 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1904,7 +1922,7 @@
         <v>5010</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>10</v>
@@ -1923,6 +1941,7 @@
   <hyperlinks>
     <hyperlink ref="H12" r:id="rId1" display="Rem chronicle【レムクロニクル】 https://www.youtube.com/@Remchronicle_BGM"/>
     <hyperlink ref="H10" r:id="rId1" display="Rem chronicle【レムクロニクル】 https://www.youtube.com/@Remchronicle_BGM"/>
+    <hyperlink ref="I11" r:id="rId2" display="https://free-guitar-sounds.work/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -260,8 +260,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -296,7 +296,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,6 +344,74 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -323,105 +422,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -432,187 +432,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,6 +623,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -641,50 +665,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -706,15 +691,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -723,6 +699,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -731,25 +731,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -758,118 +758,118 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
